--- a/Gebeurtenissen/Gebeurtenissen overzicht.xlsx
+++ b/Gebeurtenissen/Gebeurtenissen overzicht.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\duo.local\HomeDrives\in770hou\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\duo.local\HomeDrives\in770hou\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85626413-F450-4F63-90E0-8F8B29DD3913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0FB34E3-5B88-42A5-8CA4-C3C716FC7D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15840" xr2:uid="{EF441A01-9286-48D1-BA6D-1F92EDF4F85B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EF441A01-9286-48D1-BA6D-1F92EDF4F85B}"/>
   </bookViews>
   <sheets>
     <sheet name="Revisie" sheetId="2" r:id="rId1"/>
@@ -39,8 +39,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={29CC4E3A-C59B-4AA5-8AFC-3362101A8A30}</author>
+  </authors>
+  <commentList>
+    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{29CC4E3A-C59B-4AA5-8AFC-3362101A8A30}">
+      <text>
+        <t>[Opmerkingenthread]
+U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
+Opmerking:
+    Volgens mij klopt deze niet, want er is bij een ingediend verzoek nog geen beoordeling. Dit zou een attentiesignaal kunnen zijn.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
   <si>
     <t>SS101</t>
   </si>
@@ -213,9 +231,6 @@
     <t>Gebeurtenisomschrijving</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
     <t>Inburgeringsplicht API</t>
   </si>
   <si>
@@ -228,22 +243,9 @@
     <t>Examenresultaten API</t>
   </si>
   <si>
-    <t>Beoordeling aanvraag verlenging API</t>
-  </si>
-  <si>
     <t>Beschikking  voldaan inburgeringsplicht API</t>
   </si>
   <si>
-    <t>Eindoordeel vrijstelling API</t>
-  </si>
-  <si>
-    <t>Beslissing ontheffing (inclusief BIO) API</t>
-  </si>
-  <si>
-    <t>Inspanning inburgeraar
- bij instelling API</t>
-  </si>
-  <si>
     <t>Datum</t>
   </si>
   <si>
@@ -257,6 +259,42 @@
   </si>
   <si>
     <t>Initiële versie</t>
+  </si>
+  <si>
+    <t>SS112</t>
+  </si>
+  <si>
+    <t>Verzoek verlenging ingediend</t>
+  </si>
+  <si>
+    <t>SS198</t>
+  </si>
+  <si>
+    <t>Boete opgelegd na termijnoverschrijding</t>
+  </si>
+  <si>
+    <t>SS199</t>
+  </si>
+  <si>
+    <t>Uitslag examen bekend</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Bijgewerkte versie</t>
+  </si>
+  <si>
+    <t>Verlenging API</t>
+  </si>
+  <si>
+    <t>Boete API</t>
+  </si>
+  <si>
+    <t>Ontheffing API</t>
+  </si>
+  <si>
+    <t>Vrijstelling API</t>
   </si>
 </sst>
 </file>
@@ -359,13 +397,15 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Houwen, Boelo" id="{E63BC7C4-FA4C-4E7A-B53E-4A77879C9418}" userId="S::boelo.houwen@duo.nl::9229f8b1-a0e9-4221-96f9-ea23f568969c" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Thema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -403,7 +443,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -509,7 +549,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -651,15 +691,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A12" dT="2024-12-18T10:01:39.89" personId="{E63BC7C4-FA4C-4E7A-B53E-4A77879C9418}" id="{29CC4E3A-C59B-4AA5-8AFC-3362101A8A30}">
+    <text>Volgens mij klopt deze niet, want er is bij een ingediend verzoek nog geen beoordeling. Dit zou een attentiesignaal kunnen zijn.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C5B27A-2024-485B-A33A-31BE9E5F226F}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
@@ -668,24 +716,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B2" s="5">
         <v>45601</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="5">
+        <v>45817</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -694,8 +753,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6371617C-2A9F-451D-B9C0-AAD0148E374B}">
-  <dimension ref="A1:K28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6371617C-2A9F-451D-B9C0-AAD0148E374B}">
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -710,31 +769,31 @@
         <v>56</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -758,42 +817,38 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="E4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -802,10 +857,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -814,57 +869,59 @@
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -875,23 +932,25 @@
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4" t="s">
         <v>2</v>
@@ -901,31 +960,29 @@
     </row>
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>2</v>
@@ -935,75 +992,73 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
-      <c r="I11" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>2</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="H12" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>2</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1019,10 +1074,10 @@
     </row>
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -1038,15 +1093,17 @@
     </row>
     <row r="17" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4" t="s">
@@ -1055,38 +1112,38 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
-      <c r="I18" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="K18" s="4"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1095,14 +1152,16 @@
       </c>
       <c r="K19" s="4"/>
     </row>
-    <row r="20" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="4"/>
+        <v>40</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="s">
@@ -1111,25 +1170,25 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="F21" s="4" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -1137,23 +1196,19 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="4"/>
-      <c r="E22" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -1162,10 +1217,10 @@
     </row>
     <row r="23" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>2</v>
@@ -1179,19 +1234,21 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -1209,7 +1266,9 @@
         <v>2</v>
       </c>
       <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="F25" s="4" t="s">
         <v>2</v>
       </c>
@@ -1284,8 +1343,68 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
+    <row r="29" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{6371617C-2A9F-451D-B9C0-AAD0148E374B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Gebeurtenissen/Gebeurtenissen overzicht.xlsx
+++ b/Gebeurtenissen/Gebeurtenissen overzicht.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\duo.local\HomeDrives\in770hou\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0FB34E3-5B88-42A5-8CA4-C3C716FC7D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5DBCF43-9A87-4D01-BCF6-1ACFDC10CC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EF441A01-9286-48D1-BA6D-1F92EDF4F85B}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Overzicht " sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Overzicht '!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Overzicht '!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,26 +39,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={29CC4E3A-C59B-4AA5-8AFC-3362101A8A30}</author>
-  </authors>
-  <commentList>
-    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{29CC4E3A-C59B-4AA5-8AFC-3362101A8A30}">
-      <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
-    Volgens mij klopt deze niet, want er is bij een ingediend verzoek nog geen beoordeling. Dit zou een attentiesignaal kunnen zijn.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="82">
   <si>
     <t>SS101</t>
   </si>
@@ -243,9 +225,6 @@
     <t>Examenresultaten API</t>
   </si>
   <si>
-    <t>Beschikking  voldaan inburgeringsplicht API</t>
-  </si>
-  <si>
     <t>Datum</t>
   </si>
   <si>
@@ -285,13 +264,25 @@
     <t>Bijgewerkte versie</t>
   </si>
   <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>SS141</t>
+  </si>
+  <si>
+    <t>Het Inburgeringscertificaat is nu te downloaden via de Portal Inburgering</t>
+  </si>
+  <si>
     <t>Verlenging API</t>
   </si>
   <si>
-    <t>Boete API</t>
-  </si>
-  <si>
     <t>Ontheffing API</t>
+  </si>
+  <si>
+    <t>Boete api</t>
+  </si>
+  <si>
+    <t>SS141 toegevoegd, 'beschikking voldaan inburgeringsplicht' gebeurtenissen verhuist naar de Inburgeringsplicht API</t>
   </si>
   <si>
     <t>Vrijstelling API</t>
@@ -317,7 +308,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -360,11 +351,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -379,6 +383,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -397,9 +407,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Houwen, Boelo" id="{E63BC7C4-FA4C-4E7A-B53E-4A77879C9418}" userId="S::boelo.houwen@duo.nl::9229f8b1-a0e9-4221-96f9-ea23f568969c" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -697,54 +705,57 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A12" dT="2024-12-18T10:01:39.89" personId="{E63BC7C4-FA4C-4E7A-B53E-4A77879C9418}" id="{29CC4E3A-C59B-4AA5-8AFC-3362101A8A30}">
-    <text>Volgens mij klopt deze niet, want er is bij een ingediend verzoek nog geen beoordeling. Dit zou een attentiesignaal kunnen zijn.</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C5B27A-2024-485B-A33A-31BE9E5F226F}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" t="s">
         <v>62</v>
-      </c>
-      <c r="C1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" s="5">
         <v>45601</v>
       </c>
-      <c r="C2" t="s">
-        <v>66</v>
+      <c r="C2" s="7" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46182</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="5">
-        <v>45817</v>
-      </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>74</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -753,15 +764,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6371617C-2A9F-451D-B9C0-AAD0148E374B}">
-  <dimension ref="A1:K31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6371617C-2A9F-451D-B9C0-AAD0148E374B}">
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="138.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="92.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>55</v>
       </c>
@@ -781,22 +792,19 @@
         <v>60</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>78</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -815,9 +823,8 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -834,9 +841,8 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -853,9 +859,8 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -868,76 +873,72 @@
         <v>2</v>
       </c>
       <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="G5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
@@ -951,14 +952,13 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="H9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -975,9 +975,8 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
@@ -994,28 +993,26 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="G12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -1026,15 +1023,14 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="G13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
@@ -1046,14 +1042,13 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="H14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="4"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
@@ -1065,14 +1060,13 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="H15" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" s="4"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
@@ -1084,14 +1078,13 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="H16" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
@@ -1105,14 +1098,13 @@
         <v>2</v>
       </c>
       <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="H17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="4"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
@@ -1125,13 +1117,12 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K18" s="4"/>
-    </row>
-    <row r="19" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="I18" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
@@ -1146,13 +1137,12 @@
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K19" s="4"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>39</v>
       </c>
@@ -1171,9 +1161,8 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-    </row>
-    <row r="21" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1194,9 +1183,8 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-    </row>
-    <row r="22" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
@@ -1213,9 +1201,8 @@
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-    </row>
-    <row r="23" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>
@@ -1232,9 +1219,8 @@
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-    </row>
-    <row r="24" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,9 +1239,8 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-    </row>
-    <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>47</v>
       </c>
@@ -1273,14 +1258,13 @@
         <v>2</v>
       </c>
       <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="H25" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" s="4"/>
       <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-    </row>
-    <row r="26" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
@@ -1298,14 +1282,13 @@
         <v>2</v>
       </c>
       <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="H26" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" s="4"/>
       <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>51</v>
       </c>
@@ -1322,9 +1305,8 @@
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-    </row>
-    <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>53</v>
       </c>
@@ -1341,9 +1323,8 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-    </row>
-    <row r="29" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1362,16 +1343,17 @@
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-    </row>
-    <row r="30" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -1379,32 +1361,45 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-      <c r="K30" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
+      <c r="J31" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{6371617C-2A9F-451D-B9C0-AAD0148E374B}"/>
+  <autoFilter ref="A1:J1" xr:uid="{6371617C-2A9F-451D-B9C0-AAD0148E374B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>